--- a/toolkit/should-cost-buildup.xlsx
+++ b/toolkit/should-cost-buildup.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>100000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
